--- a/data/trans_dic/P02E$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,21; 92,3</t>
+          <t>79,79; 92,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,94; 95,22</t>
+          <t>86,75; 95,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,93; 92,07</t>
+          <t>82,11; 92,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,55; 93,31</t>
+          <t>85,27; 93,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,75; 92,76</t>
+          <t>85,78; 92,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,9; 93,92</t>
+          <t>86,0; 93,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,84; 91,99</t>
+          <t>84,6; 91,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,33; 92,85</t>
+          <t>87,58; 92,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,28; 91,8</t>
+          <t>85,46; 92,06</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,01; 94,7</t>
+          <t>85,91; 94,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,71; 95,56</t>
+          <t>90,04; 95,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,48; 97,26</t>
+          <t>91,34; 97,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,27; 93,96</t>
+          <t>86,75; 93,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,47; 93,94</t>
+          <t>88,54; 93,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,55; 91,72</t>
+          <t>84,65; 91,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,19; 93,42</t>
+          <t>88,2; 93,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,07; 93,94</t>
+          <t>89,83; 93,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,29; 93,15</t>
+          <t>88,39; 93,14</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,21; 94,39</t>
+          <t>83,52; 94,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,62; 95,24</t>
+          <t>88,1; 95,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,85; 95,66</t>
+          <t>87,06; 95,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,72; 93,94</t>
+          <t>86,03; 94,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,07; 96,19</t>
+          <t>91,09; 96,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,14; 92,22</t>
+          <t>83,59; 92,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,33; 92,94</t>
+          <t>86,4; 92,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,75; 95,27</t>
+          <t>90,94; 95,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,93; 92,92</t>
+          <t>86,71; 92,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 93,39</t>
+          <t>85,44; 93,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,06; 92,23</t>
+          <t>83,73; 92,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,98; 93,68</t>
+          <t>84,9; 93,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91,01; 97,13</t>
+          <t>91,29; 97,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,04; 93,58</t>
+          <t>87,69; 93,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,01; 88,31</t>
+          <t>79,46; 87,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,69; 95,42</t>
+          <t>90,71; 95,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,55; 92,16</t>
+          <t>87,6; 92,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,77; 89,24</t>
+          <t>83,09; 89,11</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>87,2; 92,21</t>
+          <t>86,69; 91,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,52; 93,02</t>
+          <t>89,42; 93,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,27; 93,29</t>
+          <t>89,32; 93,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,69; 93,36</t>
+          <t>89,92; 93,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,06; 93,08</t>
+          <t>90,16; 93,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,53; 89,65</t>
+          <t>85,62; 89,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,37; 92,3</t>
+          <t>89,42; 92,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,37; 92,68</t>
+          <t>90,47; 92,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,71; 90,44</t>
+          <t>87,64; 90,46</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>105251; 121124</t>
+          <t>104701; 121016</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172815; 189275</t>
+          <t>172435; 189658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131405; 147665</t>
+          <t>131693; 148188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>185980; 205250</t>
+          <t>187579; 205673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>255872; 276777</t>
+          <t>255954; 277056</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>167098; 184852</t>
+          <t>169260; 184330</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>297948; 323075</t>
+          <t>297115; 322336</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>434169; 461638</t>
+          <t>435429; 461893</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>304618; 327903</t>
+          <t>305287; 328842</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>169322; 186432</t>
+          <t>169128; 185953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>272437; 290195</t>
+          <t>273439; 290317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217548; 231295</t>
+          <t>217236; 231269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>267116; 287583</t>
+          <t>265512; 287520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>405078; 430137</t>
+          <t>405380; 430082</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>302817; 328485</t>
+          <t>303179; 329173</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>443531; 469823</t>
+          <t>443569; 470003</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>685913; 715383</t>
+          <t>684084; 715425</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>526162; 555125</t>
+          <t>526769; 555101</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106287; 120575</t>
+          <t>106692; 120830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>193381; 210199</t>
+          <t>194422; 210400</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142443; 156887</t>
+          <t>142778; 156912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169365; 185616</t>
+          <t>169985; 186094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>322948; 341124</t>
+          <t>323022; 341441</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>213584; 234084</t>
+          <t>212193; 234151</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>280847; 302364</t>
+          <t>281097; 301835</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>522105; 548129</t>
+          <t>523180; 547660</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>363232; 388259</t>
+          <t>362297; 387760</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>144331; 159104</t>
+          <t>145560; 159829</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>219944; 241333</t>
+          <t>219092; 241135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165237; 182158</t>
+          <t>165093; 182083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>256815; 274076</t>
+          <t>257601; 274169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>357439; 379966</t>
+          <t>356019; 380543</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>238752; 266873</t>
+          <t>240128; 265757</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>410402; 431831</t>
+          <t>410482; 430934</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>584567; 615308</t>
+          <t>584856; 617106</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>411043; 443224</t>
+          <t>412640; 442540</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>546033; 577409</t>
+          <t>542866; 575356</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>881615; 916099</t>
+          <t>880605; 917356</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>675488; 705880</t>
+          <t>675867; 707739</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>902148; 938991</t>
+          <t>904399; 938538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1366090; 1411974</t>
+          <t>1367614; 1410901</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>950221; 995994</t>
+          <t>951264; 995468</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1458464; 1506307</t>
+          <t>1459284; 1507798</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2260750; 2318630</t>
+          <t>2263198; 2319630</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1638097; 1689040</t>
+          <t>1636825; 1689541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,79; 92,22</t>
+          <t>79,83; 92,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,75; 95,41</t>
+          <t>86,64; 95,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,11; 92,39</t>
+          <t>81,37; 91,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,27; 93,5</t>
+          <t>84,7; 93,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,78; 92,85</t>
+          <t>85,07; 92,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,0; 93,65</t>
+          <t>85,65; 93,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,6; 91,78</t>
+          <t>85,02; 91,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,58; 92,9</t>
+          <t>87,58; 92,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,46; 92,06</t>
+          <t>85,57; 91,96</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,91; 94,46</t>
+          <t>85,39; 94,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,04; 95,6</t>
+          <t>89,29; 95,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,34; 97,25</t>
+          <t>90,55; 97,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,75; 93,94</t>
+          <t>87,32; 93,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,54; 93,93</t>
+          <t>88,58; 94,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,65; 91,91</t>
+          <t>84,92; 91,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,2; 93,45</t>
+          <t>88,13; 93,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,83; 93,94</t>
+          <t>90,23; 94,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,39; 93,14</t>
+          <t>88,5; 93,19</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,52; 94,59</t>
+          <t>83,64; 94,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,1; 95,33</t>
+          <t>87,87; 95,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,06; 95,67</t>
+          <t>86,49; 95,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,03; 94,18</t>
+          <t>85,79; 94,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,09; 96,28</t>
+          <t>91,16; 96,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,59; 92,24</t>
+          <t>84,32; 92,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,4; 92,78</t>
+          <t>86,49; 93,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,94; 95,19</t>
+          <t>90,73; 95,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,71; 92,8</t>
+          <t>86,69; 92,73</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,44; 93,81</t>
+          <t>85,29; 94,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,73; 92,16</t>
+          <t>84,04; 92,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,9; 93,64</t>
+          <t>84,99; 93,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91,29; 97,17</t>
+          <t>91,68; 97,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,69; 93,73</t>
+          <t>88,31; 94,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,46; 87,94</t>
+          <t>79,28; 87,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,71; 95,23</t>
+          <t>90,33; 95,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,6; 92,43</t>
+          <t>87,57; 92,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,09; 89,11</t>
+          <t>83,23; 89,42</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,88</t>
+          <t>87,12; 92,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,42; 93,15</t>
+          <t>89,47; 93,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,32; 93,53</t>
+          <t>89,18; 93,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,92; 93,31</t>
+          <t>89,79; 93,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,16; 93,01</t>
+          <t>90,09; 92,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,62; 89,6</t>
+          <t>85,51; 89,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,42; 92,39</t>
+          <t>89,36; 92,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,47; 92,72</t>
+          <t>90,32; 92,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,64; 90,46</t>
+          <t>87,63; 90,59</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104701; 121016</t>
+          <t>104755; 120728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172435; 189658</t>
+          <t>172210; 189827</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131693; 148188</t>
+          <t>130507; 147282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>187579; 205673</t>
+          <t>186320; 205159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>255954; 277056</t>
+          <t>253838; 276396</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>169260; 184330</t>
+          <t>168582; 184802</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>297115; 322336</t>
+          <t>298585; 321811</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>435429; 461893</t>
+          <t>435430; 461478</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>305287; 328842</t>
+          <t>305660; 328489</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>169128; 185953</t>
+          <t>168100; 186040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273439; 290317</t>
+          <t>271161; 290236</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217236; 231269</t>
+          <t>215341; 230905</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265512; 287520</t>
+          <t>267278; 287552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>405380; 430082</t>
+          <t>405589; 430457</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>303179; 329173</t>
+          <t>304146; 328660</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>443569; 470003</t>
+          <t>443259; 469615</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>684084; 715425</t>
+          <t>687127; 716285</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>526769; 555101</t>
+          <t>527407; 555344</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106692; 120830</t>
+          <t>106846; 120787</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>194422; 210400</t>
+          <t>193928; 210338</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142778; 156912</t>
+          <t>141844; 156382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169985; 186094</t>
+          <t>169505; 186292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>323022; 341441</t>
+          <t>323288; 341511</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>212193; 234151</t>
+          <t>214045; 233787</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>281097; 301835</t>
+          <t>281379; 303079</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>523180; 547660</t>
+          <t>521993; 547685</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>362297; 387760</t>
+          <t>362231; 387473</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>145560; 159829</t>
+          <t>145309; 160374</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>219092; 241135</t>
+          <t>219892; 241087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165093; 182083</t>
+          <t>165270; 182569</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257601; 274169</t>
+          <t>258704; 274269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>356019; 380543</t>
+          <t>358567; 381760</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240128; 265757</t>
+          <t>239564; 265673</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>410482; 430934</t>
+          <t>408791; 430778</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>584856; 617106</t>
+          <t>584653; 617051</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>412640; 442540</t>
+          <t>413335; 444086</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>542866; 575356</t>
+          <t>545566; 576200</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>880605; 917356</t>
+          <t>881128; 917470</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>675867; 707739</t>
+          <t>674813; 705713</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>904399; 938538</t>
+          <t>903129; 938878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1367614; 1410901</t>
+          <t>1366515; 1409518</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>951264; 995468</t>
+          <t>950051; 994923</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1459284; 1507798</t>
+          <t>1458314; 1506480</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2263198; 2319630</t>
+          <t>2259547; 2316987</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1636825; 1689541</t>
+          <t>1636538; 1691819</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
